--- a/src/test/resources/TestData/opencarttestdata.xlsx
+++ b/src/test/resources/TestData/opencarttestdata.xlsx
@@ -1,23 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\40034954\eclipse-workspace\TestNGPOMSeries\src\test\resources\TestData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D95EFB-3B39-4704-9B0C-A2E337B701B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{09B6B63A-D64A-4DF5-9D6C-B291153C80B4}"/>
+    <workbookView xWindow="0" yWindow="2445" windowWidth="15120" windowHeight="6495"/>
   </bookViews>
   <sheets>
     <sheet name="product" sheetId="1" r:id="rId1"/>
     <sheet name="Registration" sheetId="2" r:id="rId2"/>
     <sheet name="login" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:J21"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -91,8 +86,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,7 +209,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -266,7 +261,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -480,23 +475,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1784800-7C06-45CB-8F12-2196B99E9084}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -507,7 +502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -518,7 +513,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -529,7 +524,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -540,7 +535,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -551,7 +546,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -568,18 +563,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF72E679-8262-4F83-BB72-C0550458AB0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F834F6-42DA-462A-89CA-8675A27F9E96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
